--- a/dados/aniversariantes.xlsx
+++ b/dados/aniversariantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa-my.sharepoint.com/personal/andrefelix_energisa_com_br/Documents/Área de Trabalho/Pastas para o Github/Report-Aniversariantes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{264BCADC-59E3-4CA3-89FA-7C6015D7E585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{264BCADC-59E3-4CA3-89FA-7C6015D7E585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A08E2732-1D0F-4B66-85F9-4DF7224145C0}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{206A991C-80BF-47D0-8E2C-015A647B71BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{206A991C-80BF-47D0-8E2C-015A647B71BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/dados/aniversariantes.xlsx
+++ b/dados/aniversariantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa-my.sharepoint.com/personal/andrefelix_energisa_com_br/Documents/Área de Trabalho/Pastas para o Github/Report-Aniversariantes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{264BCADC-59E3-4CA3-89FA-7C6015D7E585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A08E2732-1D0F-4B66-85F9-4DF7224145C0}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{264BCADC-59E3-4CA3-89FA-7C6015D7E585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9CA5FE-6D0B-4B2C-A7FE-8761F224120B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{206A991C-80BF-47D0-8E2C-015A647B71BD}"/>
   </bookViews>
@@ -1779,6 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49717D36-86B4-4DB2-898B-8E964F35BEB2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J417"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1827,7 +1828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>20</v>
       </c>
@@ -1856,7 +1857,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>20</v>
       </c>
@@ -1885,7 +1886,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>20</v>
       </c>
@@ -1914,7 +1915,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1944,7 +1945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>20</v>
       </c>
@@ -1974,7 +1975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>20</v>
       </c>
@@ -2003,7 +2004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>20</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
@@ -2062,7 +2063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>20</v>
       </c>
@@ -2092,7 +2093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20</v>
       </c>
@@ -2121,7 +2122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>20</v>
       </c>
@@ -2151,7 +2152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>20</v>
       </c>
@@ -2180,7 +2181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>20</v>
       </c>
@@ -2210,7 +2211,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>20</v>
       </c>
@@ -2239,7 +2240,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>20</v>
       </c>
@@ -2268,7 +2269,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>20</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>20</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>20</v>
       </c>
@@ -2358,7 +2359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2446,7 +2447,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -2476,7 +2477,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2506,7 +2507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>20</v>
       </c>
@@ -2536,7 +2537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>20</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>20</v>
       </c>
@@ -2595,7 +2596,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>20</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>20</v>
       </c>
@@ -2654,7 +2655,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>20</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>20</v>
       </c>
@@ -2713,7 +2714,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>20</v>
       </c>
@@ -2742,7 +2743,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>20</v>
       </c>
@@ -2771,7 +2772,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>20</v>
       </c>
@@ -2801,7 +2802,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>20</v>
       </c>
@@ -2830,7 +2831,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>20</v>
       </c>
@@ -2859,7 +2860,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>20</v>
       </c>
@@ -2889,7 +2890,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>20</v>
       </c>
@@ -2918,7 +2919,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>20</v>
       </c>
@@ -2948,7 +2949,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>20</v>
       </c>
@@ -2978,7 +2979,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>20</v>
       </c>
@@ -3007,7 +3008,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>20</v>
       </c>
@@ -3037,7 +3038,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>20</v>
       </c>
@@ -3071,31 +3072,31 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>3001366</v>
+        <v>22342</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="D44" s="1">
-        <v>33907</v>
+        <v>25849</v>
       </c>
       <c r="E44" s="1">
-        <v>42383</v>
+        <v>37685</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="I44">
-        <v>190600031</v>
+        <v>190600043</v>
       </c>
       <c r="J44" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>20</v>
       </c>
@@ -3124,7 +3125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>20</v>
       </c>
@@ -3153,7 +3154,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>20</v>
       </c>
@@ -3182,7 +3183,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>20</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>20</v>
       </c>
@@ -3240,7 +3241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>20</v>
       </c>
@@ -3269,7 +3270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>20</v>
       </c>
@@ -3299,7 +3300,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>20</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>20</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>20</v>
       </c>
@@ -3387,7 +3388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>20</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>20</v>
       </c>
@@ -3446,7 +3447,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>20</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>20</v>
       </c>
@@ -3504,7 +3505,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>20</v>
       </c>
@@ -3533,7 +3534,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>20</v>
       </c>
@@ -3562,7 +3563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>20</v>
       </c>
@@ -3591,7 +3592,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>20</v>
       </c>
@@ -3620,7 +3621,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>20</v>
       </c>
@@ -3650,7 +3651,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>20</v>
       </c>
@@ -3679,7 +3680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>20</v>
       </c>
@@ -3708,7 +3709,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>20</v>
       </c>
@@ -3737,7 +3738,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>20</v>
       </c>
@@ -3767,7 +3768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>20</v>
       </c>
@@ -3796,7 +3797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>20</v>
       </c>
@@ -3830,16 +3831,16 @@
         <v>20</v>
       </c>
       <c r="B70">
-        <v>33197</v>
+        <v>21578</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="D70" s="1">
-        <v>32790</v>
+        <v>26213</v>
       </c>
       <c r="E70" s="1">
-        <v>41535</v>
+        <v>37655</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3848,13 +3849,13 @@
         <v>11</v>
       </c>
       <c r="I70">
-        <v>190612000</v>
+        <v>190600039</v>
       </c>
       <c r="J70" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>20</v>
       </c>
@@ -3883,7 +3884,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>20</v>
       </c>
@@ -3913,7 +3914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>20</v>
       </c>
@@ -3942,7 +3943,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>20</v>
       </c>
@@ -3976,28 +3977,28 @@
         <v>20</v>
       </c>
       <c r="B75">
-        <v>3001410</v>
+        <v>23371</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D75" s="1">
-        <v>34986</v>
+        <v>27329</v>
       </c>
       <c r="E75" s="1">
-        <v>42633</v>
+        <v>37693</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I75">
-        <v>190600043</v>
+        <v>190600035</v>
       </c>
       <c r="J75" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -4005,32 +4006,32 @@
         <v>20</v>
       </c>
       <c r="B76">
-        <v>27891</v>
+        <v>22125</v>
       </c>
       <c r="C76" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="D76" s="1">
-        <v>30602</v>
+        <v>28060</v>
       </c>
       <c r="E76" s="1">
-        <v>39730</v>
+        <v>37655</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I76">
-        <v>190600032</v>
+        <v>190600037</v>
       </c>
       <c r="J76" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>20</v>
       </c>
@@ -4060,7 +4061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>20</v>
       </c>
@@ -4094,31 +4095,31 @@
         <v>20</v>
       </c>
       <c r="B79">
-        <v>33550</v>
+        <v>21886</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="D79" s="1">
-        <v>30963</v>
+        <v>29148</v>
       </c>
       <c r="E79" s="1">
-        <v>41722</v>
+        <v>37655</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="I79">
-        <v>190600039</v>
+        <v>190600033</v>
       </c>
       <c r="J79" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>20</v>
       </c>
@@ -4147,7 +4148,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>20</v>
       </c>
@@ -4176,7 +4177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>20</v>
       </c>
@@ -4206,7 +4207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>20</v>
       </c>
@@ -4235,7 +4236,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>20</v>
       </c>
@@ -4264,7 +4265,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>20</v>
       </c>
@@ -4294,7 +4295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>20</v>
       </c>
@@ -4328,17 +4329,18 @@
         <v>20</v>
       </c>
       <c r="B87">
-        <v>33784</v>
+        <v>29687</v>
       </c>
       <c r="C87" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="D87" s="1">
-        <v>33534</v>
+        <v>29873</v>
       </c>
       <c r="E87" s="1">
-        <v>41733</v>
-      </c>
+        <v>40423</v>
+      </c>
+      <c r="F87" s="1"/>
       <c r="G87">
         <v>1</v>
       </c>
@@ -4352,7 +4354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>20</v>
       </c>
@@ -4381,7 +4383,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>20</v>
       </c>
@@ -4410,7 +4412,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>20</v>
       </c>
@@ -4439,7 +4441,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>20</v>
       </c>
@@ -4469,7 +4471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>20</v>
       </c>
@@ -4503,31 +4505,32 @@
         <v>20</v>
       </c>
       <c r="B93">
-        <v>29236</v>
+        <v>3082800</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>295</v>
       </c>
       <c r="D93" s="1">
-        <v>32081</v>
+        <v>29881</v>
       </c>
       <c r="E93" s="1">
-        <v>40294</v>
-      </c>
+        <v>45064</v>
+      </c>
+      <c r="F93" s="1"/>
       <c r="G93">
         <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="I93">
-        <v>190612000</v>
+        <v>190600023</v>
       </c>
       <c r="J93" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>20</v>
       </c>
@@ -4556,7 +4559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>20</v>
       </c>
@@ -4585,7 +4588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>20</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>20</v>
       </c>
@@ -4644,7 +4647,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>20</v>
       </c>
@@ -4674,7 +4677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>20</v>
       </c>
@@ -4703,7 +4706,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>20</v>
       </c>
@@ -4732,7 +4735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>20</v>
       </c>
@@ -4761,7 +4764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>20</v>
       </c>
@@ -4790,7 +4793,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>20</v>
       </c>
@@ -4819,7 +4822,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>20</v>
       </c>
@@ -4848,7 +4851,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>20</v>
       </c>
@@ -4882,31 +4885,32 @@
         <v>20</v>
       </c>
       <c r="B106">
-        <v>3005897</v>
+        <v>27891</v>
       </c>
       <c r="C106" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D106" s="1">
-        <v>33907</v>
+        <v>30602</v>
       </c>
       <c r="E106" s="1">
-        <v>42934</v>
-      </c>
+        <v>39730</v>
+      </c>
+      <c r="F106" s="1"/>
       <c r="G106">
         <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="I106">
-        <v>190600031</v>
+        <v>190600032</v>
       </c>
       <c r="J106" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>20</v>
       </c>
@@ -4940,18 +4944,17 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>29687</v>
+        <v>33550</v>
       </c>
       <c r="C108" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="D108" s="1">
-        <v>29873</v>
+        <v>30963</v>
       </c>
       <c r="E108" s="1">
-        <v>40423</v>
-      </c>
-      <c r="F108" s="1"/>
+        <v>41722</v>
+      </c>
       <c r="G108">
         <v>1</v>
       </c>
@@ -4959,13 +4962,13 @@
         <v>11</v>
       </c>
       <c r="I108">
-        <v>190612000</v>
+        <v>190600039</v>
       </c>
       <c r="J108" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>20</v>
       </c>
@@ -4995,7 +4998,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>20</v>
       </c>
@@ -5024,7 +5027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>20</v>
       </c>
@@ -5058,22 +5061,23 @@
         <v>20</v>
       </c>
       <c r="B112">
-        <v>3006223</v>
+        <v>3098674</v>
       </c>
       <c r="C112" t="s">
-        <v>142</v>
+        <v>417</v>
       </c>
       <c r="D112" s="1">
-        <v>33150</v>
+        <v>31694</v>
       </c>
       <c r="E112" s="1">
-        <v>42983</v>
-      </c>
+        <v>46161</v>
+      </c>
+      <c r="F112" s="1"/>
       <c r="G112">
         <v>1</v>
       </c>
       <c r="H112" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I112">
         <v>190600031</v>
@@ -5082,7 +5086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>20</v>
       </c>
@@ -5111,7 +5115,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>20</v>
       </c>
@@ -5141,7 +5145,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>20</v>
       </c>
@@ -5170,7 +5174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>20</v>
       </c>
@@ -5199,7 +5203,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>20</v>
       </c>
@@ -5229,7 +5233,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>20</v>
       </c>
@@ -5259,7 +5263,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>20</v>
       </c>
@@ -5288,7 +5292,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>20</v>
       </c>
@@ -5318,7 +5322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>20</v>
       </c>
@@ -5347,7 +5351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>20</v>
       </c>
@@ -5382,31 +5386,32 @@
         <v>20</v>
       </c>
       <c r="B123">
-        <v>23371</v>
+        <v>3059850</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="D123" s="1">
-        <v>27329</v>
+        <v>32069</v>
       </c>
       <c r="E123" s="1">
-        <v>37693</v>
-      </c>
+        <v>44329</v>
+      </c>
+      <c r="F123" s="1"/>
       <c r="G123">
         <v>1</v>
       </c>
       <c r="H123" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I123">
-        <v>190600035</v>
+        <v>190600031</v>
       </c>
       <c r="J123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>20</v>
       </c>
@@ -5435,7 +5440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>20</v>
       </c>
@@ -5464,7 +5469,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>20</v>
       </c>
@@ -5494,7 +5499,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>20</v>
       </c>
@@ -5524,7 +5529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>20</v>
       </c>
@@ -5554,7 +5559,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>20</v>
       </c>
@@ -5583,7 +5588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>20</v>
       </c>
@@ -5612,7 +5617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>20</v>
       </c>
@@ -5641,7 +5646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>20</v>
       </c>
@@ -5671,7 +5676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>20</v>
       </c>
@@ -5701,7 +5706,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>20</v>
       </c>
@@ -5731,7 +5736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>20</v>
       </c>
@@ -5760,7 +5765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>20</v>
       </c>
@@ -5790,7 +5795,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>20</v>
       </c>
@@ -5819,7 +5824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>20</v>
       </c>
@@ -5848,7 +5853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>20</v>
       </c>
@@ -5877,7 +5882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>20</v>
       </c>
@@ -5907,7 +5912,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>20</v>
       </c>
@@ -5936,7 +5941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>20</v>
       </c>
@@ -5970,31 +5975,31 @@
         <v>20</v>
       </c>
       <c r="B143">
-        <v>21578</v>
+        <v>3085199</v>
       </c>
       <c r="C143" t="s">
-        <v>174</v>
+        <v>321</v>
       </c>
       <c r="D143" s="1">
-        <v>26213</v>
+        <v>32076</v>
       </c>
       <c r="E143" s="1">
-        <v>37655</v>
+        <v>45267</v>
       </c>
       <c r="G143">
         <v>1</v>
       </c>
       <c r="H143" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I143">
-        <v>190600039</v>
+        <v>190611000</v>
       </c>
       <c r="J143" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>20</v>
       </c>
@@ -6028,31 +6033,31 @@
         <v>20</v>
       </c>
       <c r="B145">
-        <v>21886</v>
+        <v>29236</v>
       </c>
       <c r="C145" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="D145" s="1">
-        <v>29148</v>
+        <v>32081</v>
       </c>
       <c r="E145" s="1">
-        <v>37655</v>
+        <v>40294</v>
       </c>
       <c r="G145">
         <v>1</v>
       </c>
       <c r="H145" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="I145">
-        <v>190600033</v>
+        <v>190612000</v>
       </c>
       <c r="J145" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>20</v>
       </c>
@@ -6081,7 +6086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>20</v>
       </c>
@@ -6110,7 +6115,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>20</v>
       </c>
@@ -6139,7 +6144,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>20</v>
       </c>
@@ -6173,29 +6178,28 @@
         <v>20</v>
       </c>
       <c r="B150">
-        <v>22125</v>
+        <v>3052709</v>
       </c>
       <c r="C150" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D150" s="1">
-        <v>28060</v>
+        <v>32430</v>
       </c>
       <c r="E150" s="1">
-        <v>37655</v>
-      </c>
-      <c r="F150" s="1"/>
+        <v>43651</v>
+      </c>
       <c r="G150">
         <v>1</v>
       </c>
       <c r="H150" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I150">
-        <v>190600037</v>
+        <v>190601135</v>
       </c>
       <c r="J150" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -6203,31 +6207,32 @@
         <v>20</v>
       </c>
       <c r="B151">
-        <v>22342</v>
+        <v>3097800</v>
       </c>
       <c r="C151" t="s">
-        <v>181</v>
+        <v>415</v>
       </c>
       <c r="D151" s="1">
-        <v>25849</v>
+        <v>32437</v>
       </c>
       <c r="E151" s="1">
-        <v>37685</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="F151" s="1"/>
       <c r="G151">
         <v>1</v>
       </c>
       <c r="H151" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I151">
-        <v>190600043</v>
+        <v>190600041</v>
       </c>
       <c r="J151" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>20</v>
       </c>
@@ -6256,7 +6261,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>20</v>
       </c>
@@ -6285,7 +6290,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>20</v>
       </c>
@@ -6314,7 +6319,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>20</v>
       </c>
@@ -6343,7 +6348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>20</v>
       </c>
@@ -6373,7 +6378,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>20</v>
       </c>
@@ -6402,7 +6407,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>20</v>
       </c>
@@ -6431,7 +6436,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>20</v>
       </c>
@@ -6460,7 +6465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>20</v>
       </c>
@@ -6490,7 +6495,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>20</v>
       </c>
@@ -6519,7 +6524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>20</v>
       </c>
@@ -6549,7 +6554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>20</v>
       </c>
@@ -6579,7 +6584,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>20</v>
       </c>
@@ -6609,7 +6614,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>20</v>
       </c>
@@ -6644,16 +6649,16 @@
         <v>20</v>
       </c>
       <c r="B166">
-        <v>3052709</v>
+        <v>3078431</v>
       </c>
       <c r="C166" t="s">
-        <v>197</v>
+        <v>269</v>
       </c>
       <c r="D166" s="1">
-        <v>32430</v>
+        <v>32444</v>
       </c>
       <c r="E166" s="1">
-        <v>43651</v>
+        <v>44733</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -6662,13 +6667,13 @@
         <v>16</v>
       </c>
       <c r="I166">
-        <v>190601135</v>
+        <v>190612000</v>
       </c>
       <c r="J166" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>20</v>
       </c>
@@ -6697,7 +6702,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>20</v>
       </c>
@@ -6726,7 +6731,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>20</v>
       </c>
@@ -6755,7 +6760,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>20</v>
       </c>
@@ -6790,31 +6795,31 @@
         <v>20</v>
       </c>
       <c r="B171">
-        <v>3054943</v>
+        <v>33197</v>
       </c>
       <c r="C171" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="D171" s="1">
-        <v>33531</v>
+        <v>32790</v>
       </c>
       <c r="E171" s="1">
-        <v>43818</v>
+        <v>41535</v>
       </c>
       <c r="G171">
         <v>1</v>
       </c>
       <c r="H171" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I171">
-        <v>190600032</v>
+        <v>190612000</v>
       </c>
       <c r="J171" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>20</v>
       </c>
@@ -6843,7 +6848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>20</v>
       </c>
@@ -6873,7 +6878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>20</v>
       </c>
@@ -6902,7 +6907,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>20</v>
       </c>
@@ -6931,7 +6936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>20</v>
       </c>
@@ -6960,7 +6965,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>20</v>
       </c>
@@ -6989,7 +6994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>20</v>
       </c>
@@ -7018,7 +7023,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>20</v>
       </c>
@@ -7048,7 +7053,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>20</v>
       </c>
@@ -7077,7 +7082,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>20</v>
       </c>
@@ -7106,7 +7111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>20</v>
       </c>
@@ -7136,7 +7141,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>20</v>
       </c>
@@ -7166,7 +7171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>20</v>
       </c>
@@ -7196,7 +7201,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>20</v>
       </c>
@@ -7225,7 +7230,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>20</v>
       </c>
@@ -7254,7 +7259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>20</v>
       </c>
@@ -7283,7 +7288,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>20</v>
       </c>
@@ -7313,7 +7318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>20</v>
       </c>
@@ -7343,7 +7348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>20</v>
       </c>
@@ -7373,7 +7378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>20</v>
       </c>
@@ -7402,7 +7407,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>20</v>
       </c>
@@ -7431,7 +7436,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>20</v>
       </c>
@@ -7466,16 +7471,16 @@
         <v>20</v>
       </c>
       <c r="B194">
-        <v>3060613</v>
+        <v>3062439</v>
       </c>
       <c r="C194" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="D194" s="1">
-        <v>33534</v>
+        <v>32798</v>
       </c>
       <c r="E194" s="1">
-        <v>44390</v>
+        <v>44509</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -7490,7 +7495,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>20</v>
       </c>
@@ -7519,7 +7524,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>20</v>
       </c>
@@ -7548,7 +7553,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>20</v>
       </c>
@@ -7577,7 +7582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>20</v>
       </c>
@@ -7606,7 +7611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>20</v>
       </c>
@@ -7635,7 +7640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>20</v>
       </c>
@@ -7669,17 +7674,18 @@
         <v>20</v>
       </c>
       <c r="B201">
-        <v>3059813</v>
+        <v>3093076</v>
       </c>
       <c r="C201" t="s">
-        <v>233</v>
+        <v>439</v>
       </c>
       <c r="D201" s="1">
-        <v>36815</v>
+        <v>32804</v>
       </c>
       <c r="E201" s="1">
-        <v>44327</v>
-      </c>
+        <v>45748</v>
+      </c>
+      <c r="F201" s="1"/>
       <c r="G201">
         <v>1</v>
       </c>
@@ -7693,7 +7699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>20</v>
       </c>
@@ -7722,7 +7728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>20</v>
       </c>
@@ -7752,7 +7758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>20</v>
       </c>
@@ -7782,7 +7788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>20</v>
       </c>
@@ -7811,7 +7817,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>20</v>
       </c>
@@ -7840,7 +7846,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>20</v>
       </c>
@@ -7869,7 +7875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>20</v>
       </c>
@@ -7898,7 +7904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>20</v>
       </c>
@@ -7933,32 +7939,32 @@
         <v>20</v>
       </c>
       <c r="B210">
-        <v>3059850</v>
+        <v>3098182</v>
       </c>
       <c r="C210" t="s">
-        <v>242</v>
+        <v>409</v>
       </c>
       <c r="D210" s="1">
-        <v>32069</v>
+        <v>32805</v>
       </c>
       <c r="E210" s="1">
-        <v>44329</v>
+        <v>46126</v>
       </c>
       <c r="F210" s="1"/>
       <c r="G210">
         <v>1</v>
       </c>
       <c r="H210" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="I210">
-        <v>190600031</v>
+        <v>190600039</v>
       </c>
       <c r="J210" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>20</v>
       </c>
@@ -7988,7 +7994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>20</v>
       </c>
@@ -8017,7 +8023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>20</v>
       </c>
@@ -8046,7 +8052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>20</v>
       </c>
@@ -8075,7 +8081,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>20</v>
       </c>
@@ -8104,7 +8110,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>20</v>
       </c>
@@ -8133,7 +8139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>20</v>
       </c>
@@ -8162,7 +8168,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>20</v>
       </c>
@@ -8191,7 +8197,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>20</v>
       </c>
@@ -8220,7 +8226,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>20</v>
       </c>
@@ -8249,7 +8255,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>20</v>
       </c>
@@ -8278,7 +8284,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>20</v>
       </c>
@@ -8307,7 +8313,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>20</v>
       </c>
@@ -8336,7 +8342,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>20</v>
       </c>
@@ -8365,7 +8371,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>20</v>
       </c>
@@ -8395,7 +8401,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>20</v>
       </c>
@@ -8425,7 +8431,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>20</v>
       </c>
@@ -8454,7 +8460,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>20</v>
       </c>
@@ -8483,7 +8489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>20</v>
       </c>
@@ -8512,7 +8518,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>20</v>
       </c>
@@ -8541,7 +8547,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>20</v>
       </c>
@@ -8570,7 +8576,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>20</v>
       </c>
@@ -8599,7 +8605,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>20</v>
       </c>
@@ -8628,7 +8634,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>20</v>
       </c>
@@ -8657,7 +8663,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>20</v>
       </c>
@@ -8686,7 +8692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>20</v>
       </c>
@@ -8721,31 +8727,31 @@
         <v>20</v>
       </c>
       <c r="B237">
-        <v>3078431</v>
+        <v>3006223</v>
       </c>
       <c r="C237" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
       <c r="D237" s="1">
-        <v>32444</v>
+        <v>33150</v>
       </c>
       <c r="E237" s="1">
-        <v>44733</v>
+        <v>42983</v>
       </c>
       <c r="G237">
         <v>1</v>
       </c>
       <c r="H237" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I237">
-        <v>190612000</v>
+        <v>190600031</v>
       </c>
       <c r="J237" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>20</v>
       </c>
@@ -8775,7 +8781,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>20</v>
       </c>
@@ -8809,16 +8815,16 @@
         <v>20</v>
       </c>
       <c r="B240">
-        <v>3062439</v>
+        <v>3054943</v>
       </c>
       <c r="C240" t="s">
-        <v>272</v>
+        <v>202</v>
       </c>
       <c r="D240" s="1">
-        <v>32798</v>
+        <v>33897</v>
       </c>
       <c r="E240" s="1">
-        <v>44509</v>
+        <v>43818</v>
       </c>
       <c r="G240">
         <v>1</v>
@@ -8833,7 +8839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>20</v>
       </c>
@@ -8862,7 +8868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>20</v>
       </c>
@@ -8892,7 +8898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>20</v>
       </c>
@@ -8921,7 +8927,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>20</v>
       </c>
@@ -8951,7 +8957,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>20</v>
       </c>
@@ -8981,7 +8987,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>20</v>
       </c>
@@ -9010,7 +9016,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>20</v>
       </c>
@@ -9039,7 +9045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>20</v>
       </c>
@@ -9069,7 +9075,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>20</v>
       </c>
@@ -9103,31 +9109,31 @@
         <v>20</v>
       </c>
       <c r="B250">
-        <v>3082852</v>
+        <v>33784</v>
       </c>
       <c r="C250" t="s">
-        <v>282</v>
+        <v>117</v>
       </c>
       <c r="D250" s="1">
-        <v>35342</v>
+        <v>33534</v>
       </c>
       <c r="E250" s="1">
-        <v>45065</v>
+        <v>41733</v>
       </c>
       <c r="G250">
         <v>1</v>
       </c>
       <c r="H250" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I250">
-        <v>190600041</v>
+        <v>190612000</v>
       </c>
       <c r="J250" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>20</v>
       </c>
@@ -9156,7 +9162,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>20</v>
       </c>
@@ -9185,7 +9191,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>20</v>
       </c>
@@ -9219,16 +9225,16 @@
         <v>20</v>
       </c>
       <c r="B254">
-        <v>3085123</v>
+        <v>3060613</v>
       </c>
       <c r="C254" t="s">
-        <v>286</v>
+        <v>226</v>
       </c>
       <c r="D254" s="1">
-        <v>34626</v>
+        <v>33534</v>
       </c>
       <c r="E254" s="1">
-        <v>45265</v>
+        <v>44390</v>
       </c>
       <c r="G254">
         <v>1</v>
@@ -9237,13 +9243,13 @@
         <v>16</v>
       </c>
       <c r="I254">
-        <v>190611000</v>
+        <v>190600032</v>
       </c>
       <c r="J254" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>20</v>
       </c>
@@ -9272,7 +9278,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>20</v>
       </c>
@@ -9301,7 +9307,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>20</v>
       </c>
@@ -9330,7 +9336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>20</v>
       </c>
@@ -9359,7 +9365,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>20</v>
       </c>
@@ -9388,7 +9394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>20</v>
       </c>
@@ -9417,7 +9423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>20</v>
       </c>
@@ -9451,16 +9457,16 @@
         <v>20</v>
       </c>
       <c r="B262">
-        <v>3082800</v>
+        <v>3090096</v>
       </c>
       <c r="C262" t="s">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="D262" s="1">
-        <v>29881</v>
+        <v>33879</v>
       </c>
       <c r="E262" s="1">
-        <v>45064</v>
+        <v>45566</v>
       </c>
       <c r="F262" s="1"/>
       <c r="G262">
@@ -9470,13 +9476,13 @@
         <v>16</v>
       </c>
       <c r="I262">
-        <v>190600023</v>
+        <v>190600032</v>
       </c>
       <c r="J262" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>20</v>
       </c>
@@ -9505,7 +9511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>20</v>
       </c>
@@ -9534,7 +9540,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>20</v>
       </c>
@@ -9563,7 +9569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>20</v>
       </c>
@@ -9592,7 +9598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>20</v>
       </c>
@@ -9621,7 +9627,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>20</v>
       </c>
@@ -9650,7 +9656,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>20</v>
       </c>
@@ -9679,7 +9685,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>20</v>
       </c>
@@ -9708,7 +9714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>20</v>
       </c>
@@ -9738,7 +9744,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>20</v>
       </c>
@@ -9767,7 +9773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>20</v>
       </c>
@@ -9796,7 +9802,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>20</v>
       </c>
@@ -9825,7 +9831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>20</v>
       </c>
@@ -9854,7 +9860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>20</v>
       </c>
@@ -9883,7 +9889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>20</v>
       </c>
@@ -9912,7 +9918,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>20</v>
       </c>
@@ -9942,7 +9948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>20</v>
       </c>
@@ -9971,7 +9977,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>20</v>
       </c>
@@ -10000,7 +10006,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>20</v>
       </c>
@@ -10029,7 +10035,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>20</v>
       </c>
@@ -10058,7 +10064,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>20</v>
       </c>
@@ -10088,7 +10094,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>20</v>
       </c>
@@ -10118,7 +10124,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>20</v>
       </c>
@@ -10147,7 +10153,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>20</v>
       </c>
@@ -10181,28 +10187,29 @@
         <v>20</v>
       </c>
       <c r="B287">
-        <v>3085191</v>
+        <v>3082752</v>
       </c>
       <c r="C287" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="D287" s="1">
-        <v>37182</v>
+        <v>33906</v>
       </c>
       <c r="E287" s="1">
-        <v>45267</v>
-      </c>
+        <v>45062</v>
+      </c>
+      <c r="F287" s="1"/>
       <c r="G287">
         <v>1</v>
       </c>
       <c r="H287" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="I287">
-        <v>190600033</v>
+        <v>190600041</v>
       </c>
       <c r="J287" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
@@ -10210,31 +10217,31 @@
         <v>20</v>
       </c>
       <c r="B288">
-        <v>3085199</v>
+        <v>3001366</v>
       </c>
       <c r="C288" t="s">
-        <v>321</v>
+        <v>69</v>
       </c>
       <c r="D288" s="1">
-        <v>32076</v>
+        <v>33907</v>
       </c>
       <c r="E288" s="1">
-        <v>45267</v>
+        <v>42383</v>
       </c>
       <c r="G288">
         <v>1</v>
       </c>
       <c r="H288" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I288">
-        <v>190611000</v>
+        <v>190600031</v>
       </c>
       <c r="J288" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>20</v>
       </c>
@@ -10268,31 +10275,31 @@
         <v>20</v>
       </c>
       <c r="B290">
-        <v>3085158</v>
+        <v>3005897</v>
       </c>
       <c r="C290" t="s">
-        <v>323</v>
+        <v>136</v>
       </c>
       <c r="D290" s="1">
-        <v>36087</v>
+        <v>33907</v>
       </c>
       <c r="E290" s="1">
-        <v>45265</v>
+        <v>42934</v>
       </c>
       <c r="G290">
         <v>1</v>
       </c>
       <c r="H290" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I290">
-        <v>190612000</v>
+        <v>190600031</v>
       </c>
       <c r="J290" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>20</v>
       </c>
@@ -10321,7 +10328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>20</v>
       </c>
@@ -10351,7 +10358,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>20</v>
       </c>
@@ -10381,7 +10388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>20</v>
       </c>
@@ -10411,7 +10418,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>20</v>
       </c>
@@ -10441,7 +10448,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>20</v>
       </c>
@@ -10471,7 +10478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>20</v>
       </c>
@@ -10501,7 +10508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>20</v>
       </c>
@@ -10530,7 +10537,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>20</v>
       </c>
@@ -10559,7 +10566,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>20</v>
       </c>
@@ -10588,7 +10595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>20</v>
       </c>
@@ -10617,7 +10624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>20</v>
       </c>
@@ -10647,7 +10654,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>20</v>
       </c>
@@ -10677,7 +10684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>20</v>
       </c>
@@ -10711,16 +10718,16 @@
         <v>20</v>
       </c>
       <c r="B305">
-        <v>3082752</v>
+        <v>3087764</v>
       </c>
       <c r="C305" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="D305" s="1">
-        <v>33906</v>
+        <v>34616</v>
       </c>
       <c r="E305" s="1">
-        <v>45062</v>
+        <v>45414</v>
       </c>
       <c r="F305" s="1"/>
       <c r="G305">
@@ -10730,13 +10737,13 @@
         <v>16</v>
       </c>
       <c r="I305">
-        <v>190600041</v>
+        <v>190600031</v>
       </c>
       <c r="J305" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>20</v>
       </c>
@@ -10766,7 +10773,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>20</v>
       </c>
@@ -10796,7 +10803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>20</v>
       </c>
@@ -10825,7 +10832,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>20</v>
       </c>
@@ -10854,7 +10861,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>20</v>
       </c>
@@ -10884,7 +10891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>20</v>
       </c>
@@ -10914,7 +10921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>20</v>
       </c>
@@ -10944,7 +10951,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>20</v>
       </c>
@@ -10979,18 +10986,17 @@
         <v>20</v>
       </c>
       <c r="B314">
-        <v>3082848</v>
+        <v>3085123</v>
       </c>
       <c r="C314" t="s">
-        <v>347</v>
+        <v>286</v>
       </c>
       <c r="D314" s="1">
-        <v>35345</v>
+        <v>34626</v>
       </c>
       <c r="E314" s="1">
-        <v>45065</v>
-      </c>
-      <c r="F314" s="1"/>
+        <v>45265</v>
+      </c>
       <c r="G314">
         <v>1</v>
       </c>
@@ -10998,13 +11004,13 @@
         <v>16</v>
       </c>
       <c r="I314">
-        <v>190600041</v>
+        <v>190611000</v>
       </c>
       <c r="J314" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>20</v>
       </c>
@@ -11034,7 +11040,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>20</v>
       </c>
@@ -11064,7 +11070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>20</v>
       </c>
@@ -11094,7 +11100,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>20</v>
       </c>
@@ -11129,16 +11135,16 @@
         <v>20</v>
       </c>
       <c r="B319">
-        <v>3087764</v>
+        <v>3089346</v>
       </c>
       <c r="C319" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="D319" s="1">
-        <v>34616</v>
+        <v>34982</v>
       </c>
       <c r="E319" s="1">
-        <v>45414</v>
+        <v>45517</v>
       </c>
       <c r="F319" s="1"/>
       <c r="G319">
@@ -11148,13 +11154,13 @@
         <v>16</v>
       </c>
       <c r="I319">
-        <v>190600031</v>
+        <v>190611000</v>
       </c>
       <c r="J319" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>20</v>
       </c>
@@ -11184,7 +11190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>20</v>
       </c>
@@ -11214,7 +11220,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>20</v>
       </c>
@@ -11244,7 +11250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>20</v>
       </c>
@@ -11274,7 +11280,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>20</v>
       </c>
@@ -11304,7 +11310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>20</v>
       </c>
@@ -11334,7 +11340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>20</v>
       </c>
@@ -11364,7 +11370,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>20</v>
       </c>
@@ -11394,7 +11400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>20</v>
       </c>
@@ -11424,7 +11430,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>20</v>
       </c>
@@ -11454,7 +11460,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>20</v>
       </c>
@@ -11484,7 +11490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>20</v>
       </c>
@@ -11514,7 +11520,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>20</v>
       </c>
@@ -11544,7 +11550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>20</v>
       </c>
@@ -11579,18 +11585,17 @@
         <v>20</v>
       </c>
       <c r="B334">
-        <v>3089346</v>
+        <v>3001410</v>
       </c>
       <c r="C334" t="s">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="D334" s="1">
-        <v>34982</v>
+        <v>34986</v>
       </c>
       <c r="E334" s="1">
-        <v>45517</v>
-      </c>
-      <c r="F334" s="1"/>
+        <v>42633</v>
+      </c>
       <c r="G334">
         <v>1</v>
       </c>
@@ -11598,13 +11603,13 @@
         <v>16</v>
       </c>
       <c r="I334">
-        <v>190611000</v>
+        <v>190600043</v>
       </c>
       <c r="J334" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>20</v>
       </c>
@@ -11634,7 +11639,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>20</v>
       </c>
@@ -11664,7 +11669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>20</v>
       </c>
@@ -11699,18 +11704,17 @@
         <v>20</v>
       </c>
       <c r="B338">
-        <v>3090096</v>
+        <v>3082852</v>
       </c>
       <c r="C338" t="s">
-        <v>371</v>
+        <v>282</v>
       </c>
       <c r="D338" s="1">
-        <v>33879</v>
+        <v>35342</v>
       </c>
       <c r="E338" s="1">
-        <v>45566</v>
-      </c>
-      <c r="F338" s="1"/>
+        <v>45065</v>
+      </c>
       <c r="G338">
         <v>1</v>
       </c>
@@ -11718,13 +11722,13 @@
         <v>16</v>
       </c>
       <c r="I338">
-        <v>190600032</v>
+        <v>190600041</v>
       </c>
       <c r="J338" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>20</v>
       </c>
@@ -11754,7 +11758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>20</v>
       </c>
@@ -11784,7 +11788,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>20</v>
       </c>
@@ -11819,16 +11823,16 @@
         <v>20</v>
       </c>
       <c r="B342">
-        <v>3092137</v>
+        <v>3082848</v>
       </c>
       <c r="C342" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="D342" s="1">
-        <v>37900</v>
+        <v>35345</v>
       </c>
       <c r="E342" s="1">
-        <v>45699</v>
+        <v>45065</v>
       </c>
       <c r="F342" s="1"/>
       <c r="G342">
@@ -11838,13 +11842,13 @@
         <v>16</v>
       </c>
       <c r="I342">
-        <v>190612000</v>
+        <v>190600041</v>
       </c>
       <c r="J342" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>20</v>
       </c>
@@ -11874,7 +11878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>20</v>
       </c>
@@ -11904,7 +11908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>20</v>
       </c>
@@ -11934,7 +11938,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>20</v>
       </c>
@@ -11964,7 +11968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>20</v>
       </c>
@@ -11994,7 +11998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>20</v>
       </c>
@@ -12024,7 +12028,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>20</v>
       </c>
@@ -12054,7 +12058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>20</v>
       </c>
@@ -12084,7 +12088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>20</v>
       </c>
@@ -12114,7 +12118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>20</v>
       </c>
@@ -12144,7 +12148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>20</v>
       </c>
@@ -12174,7 +12178,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>20</v>
       </c>
@@ -12204,7 +12208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>20</v>
       </c>
@@ -12234,7 +12238,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>20</v>
       </c>
@@ -12264,7 +12268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>20</v>
       </c>
@@ -12294,7 +12298,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>20</v>
       </c>
@@ -12324,7 +12328,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>20</v>
       </c>
@@ -12354,7 +12358,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>20</v>
       </c>
@@ -12384,7 +12388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>20</v>
       </c>
@@ -12419,32 +12423,31 @@
         <v>20</v>
       </c>
       <c r="B362">
-        <v>3092805</v>
+        <v>3085158</v>
       </c>
       <c r="C362" t="s">
-        <v>388</v>
+        <v>323</v>
       </c>
       <c r="D362" s="1">
-        <v>36825</v>
+        <v>36087</v>
       </c>
       <c r="E362" s="1">
-        <v>45734</v>
-      </c>
-      <c r="F362" s="1"/>
+        <v>45265</v>
+      </c>
       <c r="G362">
         <v>1</v>
       </c>
       <c r="H362" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="I362">
-        <v>190600043</v>
+        <v>190612000</v>
       </c>
       <c r="J362" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>20</v>
       </c>
@@ -12474,7 +12477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>20</v>
       </c>
@@ -12504,7 +12507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>20</v>
       </c>
@@ -12534,7 +12537,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>20</v>
       </c>
@@ -12564,7 +12567,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>20</v>
       </c>
@@ -12594,7 +12597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>20</v>
       </c>
@@ -12624,7 +12627,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>20</v>
       </c>
@@ -12684,7 +12687,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>20</v>
       </c>
@@ -12714,7 +12717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>20</v>
       </c>
@@ -12744,7 +12747,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>20</v>
       </c>
@@ -12774,7 +12777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>20</v>
       </c>
@@ -12804,7 +12807,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>20</v>
       </c>
@@ -12834,7 +12837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>20</v>
       </c>
@@ -12864,7 +12867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>20</v>
       </c>
@@ -12894,7 +12897,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>20</v>
       </c>
@@ -12924,7 +12927,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>20</v>
       </c>
@@ -12954,7 +12957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>20</v>
       </c>
@@ -12984,7 +12987,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>20</v>
       </c>
@@ -13014,7 +13017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>20</v>
       </c>
@@ -13049,32 +13052,31 @@
         <v>20</v>
       </c>
       <c r="B383">
-        <v>3098182</v>
+        <v>3059813</v>
       </c>
       <c r="C383" t="s">
-        <v>409</v>
+        <v>233</v>
       </c>
       <c r="D383" s="1">
-        <v>32805</v>
+        <v>36815</v>
       </c>
       <c r="E383" s="1">
-        <v>46126</v>
-      </c>
-      <c r="F383" s="1"/>
+        <v>44327</v>
+      </c>
       <c r="G383">
         <v>1</v>
       </c>
       <c r="H383" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="I383">
-        <v>190600039</v>
+        <v>190600035</v>
       </c>
       <c r="J383" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>20</v>
       </c>
@@ -13104,7 +13106,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>20</v>
       </c>
@@ -13134,7 +13136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>20</v>
       </c>
@@ -13164,7 +13166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>20</v>
       </c>
@@ -13194,7 +13196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>20</v>
       </c>
@@ -13229,32 +13231,32 @@
         <v>20</v>
       </c>
       <c r="B389">
-        <v>3097800</v>
+        <v>3092805</v>
       </c>
       <c r="C389" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
       <c r="D389" s="1">
-        <v>32437</v>
+        <v>36825</v>
       </c>
       <c r="E389" s="1">
-        <v>46100</v>
+        <v>45734</v>
       </c>
       <c r="F389" s="1"/>
       <c r="G389">
         <v>1</v>
       </c>
       <c r="H389" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="I389">
-        <v>190600041</v>
+        <v>190600043</v>
       </c>
       <c r="J389" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>20</v>
       </c>
@@ -13289,32 +13291,31 @@
         <v>20</v>
       </c>
       <c r="B391">
-        <v>3098674</v>
+        <v>3085191</v>
       </c>
       <c r="C391" t="s">
-        <v>417</v>
+        <v>320</v>
       </c>
       <c r="D391" s="1">
-        <v>31694</v>
+        <v>37182</v>
       </c>
       <c r="E391" s="1">
-        <v>46161</v>
-      </c>
-      <c r="F391" s="1"/>
+        <v>45267</v>
+      </c>
       <c r="G391">
         <v>1</v>
       </c>
       <c r="H391" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="I391">
-        <v>190600031</v>
+        <v>190600033</v>
       </c>
       <c r="J391" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>20</v>
       </c>
@@ -13344,7 +13345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>20</v>
       </c>
@@ -13374,7 +13375,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>20</v>
       </c>
@@ -13404,7 +13405,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>20</v>
       </c>
@@ -13434,7 +13435,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>20</v>
       </c>
@@ -13464,7 +13465,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>20</v>
       </c>
@@ -13494,7 +13495,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>20</v>
       </c>
@@ -13524,7 +13525,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>20</v>
       </c>
@@ -13554,7 +13555,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>20</v>
       </c>
@@ -13584,7 +13585,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>20</v>
       </c>
@@ -13614,7 +13615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>20</v>
       </c>
@@ -13644,7 +13645,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>20</v>
       </c>
@@ -13674,7 +13675,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>20</v>
       </c>
@@ -13704,7 +13705,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>20</v>
       </c>
@@ -13734,7 +13735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>20</v>
       </c>
@@ -13764,7 +13765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>20</v>
       </c>
@@ -13794,7 +13795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>20</v>
       </c>
@@ -13824,7 +13825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>20</v>
       </c>
@@ -13854,7 +13855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>20</v>
       </c>
@@ -13884,7 +13885,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>20</v>
       </c>
@@ -13919,16 +13920,16 @@
         <v>20</v>
       </c>
       <c r="B412">
-        <v>3093076</v>
+        <v>3092137</v>
       </c>
       <c r="C412" t="s">
-        <v>439</v>
+        <v>375</v>
       </c>
       <c r="D412" s="1">
-        <v>32804</v>
+        <v>37900</v>
       </c>
       <c r="E412" s="1">
-        <v>45748</v>
+        <v>45699</v>
       </c>
       <c r="F412" s="1"/>
       <c r="G412">
@@ -13938,13 +13939,13 @@
         <v>16</v>
       </c>
       <c r="I412">
-        <v>190600035</v>
+        <v>190612000</v>
       </c>
       <c r="J412" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>20</v>
       </c>
@@ -13974,7 +13975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>20</v>
       </c>
@@ -14004,7 +14005,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>20</v>
       </c>
@@ -14034,7 +14035,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>20</v>
       </c>
@@ -14064,7 +14065,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>20</v>
       </c>
@@ -14095,7 +14096,38 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J417" xr:uid="{49717D36-86B4-4DB2-898B-8E964F35BEB2}"/>
+  <autoFilter ref="A1:J417" xr:uid="{49717D36-86B4-4DB2-898B-8E964F35BEB2}">
+    <filterColumn colId="3">
+      <filters>
+        <dateGroupItem year="2003" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="2001" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="2000" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1999" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1998" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1996" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1995" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1994" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1992" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1991" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1990" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1989" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1988" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1987" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1986" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1984" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1983" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1981" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1979" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1976" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1974" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="1971" dateTimeGrouping="year"/>
+        <dateGroupItem year="1970" month="10" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A44:J412">
+      <sortCondition ref="D1:D417"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>